--- a/SGC-CKN/Excel/43065c23-87ae-4ed1-adfd-5de7846c0c02_Thanh_Hoá_P2_16_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/43065c23-87ae-4ed1-adfd-5de7846c0c02_Thanh_Hoá_P2_16_D800_06-04-2026.xlsx
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -142,7 +142,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">14:10
@@ -152,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">14:35
@@ -162,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:15
@@ -175,7 +175,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:50
@@ -1259,16 +1259,16 @@
         <v>-8.9</v>
       </c>
       <c r="G14" s="16">
-        <v>-19.2</v>
+        <v>-13.2</v>
       </c>
       <c r="H14" s="16">
         <v>2.5</v>
       </c>
       <c r="I14" s="16">
-        <v>10.3</v>
+        <v>4.3</v>
       </c>
       <c r="J14" s="12">
-        <v>4.12</v>
+        <v>1.72</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1291,7 +1291,7 @@
         <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>-19.2</v>
+        <v>-13.2</v>
       </c>
       <c r="G15" s="19">
         <v>-24.2</v>
@@ -1300,10 +1300,10 @@
         <v>0.67</v>
       </c>
       <c r="I15" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J15" s="8">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1653,16 +1653,16 @@
         <v>-8.9</v>
       </c>
       <c r="F5" s="16">
-        <v>-19.2</v>
+        <v>-13.2</v>
       </c>
       <c r="G5" s="16">
         <v>2.5</v>
       </c>
       <c r="H5" s="16">
-        <v>10.3</v>
+        <v>4.3</v>
       </c>
       <c r="I5" s="12">
-        <v>4.12</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-19.2</v>
+        <v>-13.2</v>
       </c>
       <c r="F6" s="19">
         <v>-24.2</v>
@@ -1688,10 +1688,10 @@
         <v>0.67</v>
       </c>
       <c r="H6" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I6" s="8">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
